--- a/tasks_data.xlsx
+++ b/tasks_data.xlsx
@@ -910,7 +910,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46128.66029772537</v>
+        <v>46128.66029771991</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
